--- a/Configs/GameConfig/Datas/fg/#Recipe-配方.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Recipe-配方.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,30 +1042,30 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>drop_pod</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>recipe.machine.name</t>
+          <t>recipe.drop_pod.name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>assembly_station</t>
+          <t>component_workshop</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>building.assembly_station.name</t>
+          <t>building.component_workshop.name</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>blueprint</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1079,37 +1079,74 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>megastructure_part</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>recipe.megastructure_part.name</t>
+          <t>recipe.machine.name</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>megastructure_factory</t>
+          <t>assembly_station</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>building.megastructure_factory.name</t>
+          <t>building.assembly_station.name</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>blueprint</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>megastructure_part</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>recipe.megastructure_part.name</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>megastructure_factory</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>building.megastructure_factory.name</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
